--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N1_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N1_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.044250149900012</v>
+        <v>1.469690649358752</v>
       </c>
       <c r="D2" t="n">
-        <v>9.034081178278866</v>
+        <v>1.468038191470316</v>
       </c>
       <c r="E2" t="n">
-        <v>10.62508093824195</v>
+        <v>1.726575652464316</v>
       </c>
       <c r="F2" t="n">
-        <v>9.98164639525076</v>
+        <v>1.622017539228249</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.510537344230748</v>
+        <v>0.5704623184374965</v>
       </c>
       <c r="D3" t="n">
-        <v>3.773279871795175</v>
+        <v>0.6131579791667159</v>
       </c>
       <c r="E3" t="n">
-        <v>10.62508093824195</v>
+        <v>1.726575652464316</v>
       </c>
       <c r="F3" t="n">
-        <v>9.98164639525076</v>
+        <v>1.622017539228249</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.97373895108632</v>
+        <v>3.733232579551527</v>
       </c>
       <c r="D4" t="n">
-        <v>22.78861713175674</v>
+        <v>3.703150283910471</v>
       </c>
       <c r="E4" t="n">
-        <v>10.62508093824195</v>
+        <v>1.726575652464316</v>
       </c>
       <c r="F4" t="n">
-        <v>9.98164639525076</v>
+        <v>1.622017539228249</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.71828596407002</v>
+        <v>4.666721469161379</v>
       </c>
       <c r="D5" t="n">
-        <v>28.51860318494217</v>
+        <v>4.634273017553102</v>
       </c>
       <c r="E5" t="n">
-        <v>10.62508093824195</v>
+        <v>1.726575652464316</v>
       </c>
       <c r="F5" t="n">
-        <v>9.98164639525076</v>
+        <v>1.622017539228249</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.86145355719419</v>
+        <v>5.014986203044056</v>
       </c>
       <c r="D6" t="n">
-        <v>30.85027714755397</v>
+        <v>5.01317003647752</v>
       </c>
       <c r="E6" t="n">
-        <v>10.62508093824195</v>
+        <v>1.726575652464316</v>
       </c>
       <c r="F6" t="n">
-        <v>9.98164639525076</v>
+        <v>1.622017539228249</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.26194078924912</v>
+        <v>4.755065378252983</v>
       </c>
       <c r="D7" t="n">
-        <v>24.04163056034261</v>
+        <v>3.906764966055675</v>
       </c>
       <c r="E7" t="n">
-        <v>10.62508093824195</v>
+        <v>1.726575652464316</v>
       </c>
       <c r="F7" t="n">
-        <v>9.98164639525076</v>
+        <v>1.622017539228249</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
